--- a/Data/Building/Lab.Humidity.xlsx
+++ b/Data/Building/Lab.Humidity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:I152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709252577</v>
+        <v>1711844482</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709253462</v>
+        <v>1711845336</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,11 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +562,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709260294</v>
+        <v>1711851941</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +576,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +595,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709262021</v>
+        <v>1711853705</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +609,11 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +632,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709263199</v>
+        <v>1711854826</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +646,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +665,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709265051</v>
+        <v>1711856634</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +679,11 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +702,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709266354</v>
+        <v>1711857792</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +716,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +735,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709268175</v>
+        <v>1711859657</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +749,11 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +772,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709269512</v>
+        <v>1711860777</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +786,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +805,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709271309</v>
+        <v>1711862436</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +819,11 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +842,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709272603</v>
+        <v>1711863223</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +856,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +875,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709274541</v>
+        <v>1711867011</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +889,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +908,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709246593</v>
+        <v>1711925356</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +922,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +941,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709247506</v>
+        <v>1711926306</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +955,11 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +978,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709332194</v>
+        <v>1711931810</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +992,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +1011,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709333409</v>
+        <v>1711933147</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1025,11 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1048,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709340188</v>
+        <v>1711934360</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1062,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1081,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709341912</v>
+        <v>1711936061</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1095,11 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1118,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709343124</v>
+        <v>1711937083</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1132,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1151,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709344974</v>
+        <v>1711938629</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1165,11 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1188,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709346229</v>
+        <v>1711939793</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1202,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1221,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709347990</v>
+        <v>1712011559</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1235,11 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1258,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709349155</v>
+        <v>1712018848</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1272,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1291,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709350919</v>
+        <v>1712020054</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1305,11 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1328,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709352305</v>
+        <v>1712021719</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1342,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1361,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709354001</v>
+        <v>1712023098</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1375,11 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1398,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709355312</v>
+        <v>1712024231</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1412,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1431,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709419464</v>
+        <v>1712025797</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1445,11 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1468,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709511919</v>
+        <v>1712026868</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1482,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1501,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709512766</v>
+        <v>1712028649</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1515,11 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1538,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709514977</v>
+        <v>1712029627</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1552,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1571,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709516234</v>
+        <v>1712035603</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1585,11 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1608,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709518186</v>
+        <v>1712105588</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1622,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1641,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709519512</v>
+        <v>1712107311</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1655,11 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1678,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709521463</v>
+        <v>1712108483</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1692,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1711,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709522626</v>
+        <v>1712110388</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1725,11 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1748,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709524499</v>
+        <v>1712111481</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1762,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1781,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709525625</v>
+        <v>1712113331</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1795,11 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1818,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709527297</v>
+        <v>1712114418</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1832,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1851,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709528387</v>
+        <v>1712116023</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1865,11 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1888,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709594892</v>
+        <v>1712117157</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1902,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1921,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709595823</v>
+        <v>1712119153</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1935,11 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1958,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709601721</v>
+        <v>1712120228</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1972,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1991,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709602922</v>
+        <v>1712122351</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1873,10 +2001,11 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lab.Humidity.state: ExcessivelyHumid</t>
+          <t>Lab.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +2024,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709604866</v>
+        <v>1712182046</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +2038,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +2057,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709606084</v>
+        <v>1712182805</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +2071,11 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2094,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709607978</v>
+        <v>1712275986</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2108,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2127,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709609105</v>
+        <v>1712276905</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2141,11 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2164,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709610969</v>
+        <v>1712278897</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2178,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2197,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709612251</v>
+        <v>1712280099</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2211,11 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2234,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709614195</v>
+        <v>1712281841</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2248,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2267,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709615365</v>
+        <v>1712282971</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2281,11 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2304,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709617736</v>
+        <v>1712284717</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2318,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2337,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709850650</v>
+        <v>1712285869</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2351,11 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2374,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709944235</v>
+        <v>1712287811</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2388,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2407,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709945381</v>
+        <v>1712289045</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2421,11 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2444,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709947346</v>
+        <v>1712290777</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2458,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2477,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709948457</v>
+        <v>1712531920</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2491,11 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2514,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709950302</v>
+        <v>1712550281</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2528,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2547,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709951423</v>
+        <v>1712551082</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2561,11 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2584,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709953281</v>
+        <v>1712625685</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2598,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2617,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709954370</v>
+        <v>1712626811</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2631,11 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2654,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710030133</v>
+        <v>1712628547</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2668,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2687,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710031449</v>
+        <v>1712629742</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2701,11 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2724,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710033291</v>
+        <v>1712631465</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2738,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2757,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710034414</v>
+        <v>1712632611</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2771,11 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2794,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710036137</v>
+        <v>1712634440</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2808,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2827,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710037398</v>
+        <v>1712635456</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2841,11 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2864,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710039226</v>
+        <v>1712713068</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2878,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2897,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710040551</v>
+        <v>1712713895</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2911,11 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2934,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710042369</v>
+        <v>1712722221</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2948,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2967,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710043543</v>
+        <v>1712723404</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2981,11 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +3004,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710045442</v>
+        <v>1712725050</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +3018,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +3037,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710046646</v>
+        <v>1712726133</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +3051,11 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +3074,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710118790</v>
+        <v>1712727745</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +3088,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3107,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710119747</v>
+        <v>1712792116</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +3121,11 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3144,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710122969</v>
+        <v>1712798153</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3158,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3177,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710123871</v>
+        <v>1712799202</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3191,11 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3214,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710127253</v>
+        <v>1712800851</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3228,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3247,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710128121</v>
+        <v>1712801941</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3261,11 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3284,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710132082</v>
+        <v>1712803896</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3298,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3317,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710132932</v>
+        <v>1712804956</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3331,11 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3354,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710203884</v>
+        <v>1712806680</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3368,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3387,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710204727</v>
+        <v>1712808017</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3401,11 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3424,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710208552</v>
+        <v>1712808969</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3438,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3457,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710209488</v>
+        <v>1712810353</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3471,11 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3494,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710213068</v>
+        <v>1712811188</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3508,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3527,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710213984</v>
+        <v>1712876394</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3541,11 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3564,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710217728</v>
+        <v>1713142554</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3578,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3597,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710218696</v>
+        <v>1713143446</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3611,11 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3634,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710464440</v>
+        <v>1713147162</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3648,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3667,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710465251</v>
+        <v>1713148043</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3681,11 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3704,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710468925</v>
+        <v>1713150975</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3718,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3737,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710469804</v>
+        <v>1713151837</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3751,11 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3774,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710473439</v>
+        <v>1713153733</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3788,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3807,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710474314</v>
+        <v>1713154588</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3821,11 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3844,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710637575</v>
+        <v>1713156434</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3858,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3877,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710638519</v>
+        <v>1713220093</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3891,11 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3914,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710642260</v>
+        <v>1713228947</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3928,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3947,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710643113</v>
+        <v>1713229854</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3961,11 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3984,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710647136</v>
+        <v>1713233359</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3998,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +4017,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710648030</v>
+        <v>1713234272</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +4031,11 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +4054,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710651916</v>
+        <v>1713237853</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +4068,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +4087,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710716431</v>
+        <v>1713238673</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3797,6 +4101,11 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +4124,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710725298</v>
+        <v>1713314340</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +4138,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4157,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710726229</v>
+        <v>1713315084</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +4171,11 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4194,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710729654</v>
+        <v>1713318778</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3893,6 +4208,7 @@
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4227,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710730523</v>
+        <v>1713319641</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4241,11 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4264,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710734357</v>
+        <v>1713323096</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4278,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4297,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710735339</v>
+        <v>1713323929</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3989,6 +4311,11 @@
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4334,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710809117</v>
+        <v>1713325595</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4348,7 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4367,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710810062</v>
+        <v>1713326376</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4381,11 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4404,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710813893</v>
+        <v>1713402621</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4418,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4437,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710814893</v>
+        <v>1713403443</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4117,6 +4451,11 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4474,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710818665</v>
+        <v>1713407117</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4488,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4507,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710819567</v>
+        <v>1713407978</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4521,11 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4544,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710823283</v>
+        <v>1713409816</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4558,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4577,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710824108</v>
+        <v>1713410656</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4591,11 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4614,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1711072717</v>
+        <v>1713412387</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4628,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4647,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1711073713</v>
+        <v>1713481029</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4661,11 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4684,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1711077745</v>
+        <v>1713489785</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4698,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4717,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1711078626</v>
+        <v>1713490638</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4731,11 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4754,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1711082547</v>
+        <v>1713494250</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4768,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4787,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1711147768</v>
+        <v>1713494979</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4801,11 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4824,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1711325761</v>
+        <v>1713496935</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4838,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4857,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1711326592</v>
+        <v>1713497859</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4501,6 +4871,11 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4894,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1711330220</v>
+        <v>1713499750</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4908,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4927,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1711331113</v>
+        <v>1713738448</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4565,6 +4941,11 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4964,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1711335050</v>
+        <v>1713746614</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4978,7 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4997,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1711335934</v>
+        <v>1713747497</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +5011,11 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +5034,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1711339993</v>
+        <v>1713750828</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4661,6 +5048,7 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +5067,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1711340839</v>
+        <v>1713751733</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +5081,11 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +5104,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1711415441</v>
+        <v>1713754668</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +5118,7 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +5137,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1711416288</v>
+        <v>1713755505</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +5151,11 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +5174,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1711420192</v>
+        <v>1713757263</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4789,6 +5188,7 @@
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +5207,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1711421052</v>
+        <v>1713825487</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4821,6 +5221,11 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5244,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1711424919</v>
+        <v>1713837990</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4853,6 +5258,7 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5277,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1711425818</v>
+        <v>1713838985</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5291,464 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1713842703</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Lab.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1713843574</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Lab.Humidity.state: ExcessivelyHumid</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1713847064</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Lab.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1713847861</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Lab.Humidity.state: ExcessivelyHumid</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1713930068</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Lab.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1713930917</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Lab.Humidity.state: ExcessivelyHumid</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1714011050</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Lab.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1714011848</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Lab.Humidity.state: ExcessivelyHumid</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1714015370</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Lab.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1714084499</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Lab.Humidity.state: ExcessivelyHumid</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1714099327</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Lab.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1714100163</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Lab.Humidity.state: ExcessivelyHumid</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1714103561</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Lab.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
